--- a/sample/order_remarks.xlsx
+++ b/sample/order_remarks.xlsx
@@ -519,7 +519,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -662,7 +662,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>3</v>
       </c>
